--- a/data/trans_camb/IP10_n_R-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP10_n_R-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-5.185176212152371</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4.168467854896027</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.830632438376699</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.632137373813616</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-1.80026008360149</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>4.935267682088885</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-10.30692538136672</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-2.817731548299127</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.998175182130734</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-0.8196259448922056</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-5.222466360902937</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-0.2142883360778129</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-0.5356503608800504</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.70944097758144</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.445412062120051</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>13.95872000599162</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.458606801836406</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>10.64954016823006</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.3416051265641897</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.2746232588611338</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.1658231036225327</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.5101725937853469</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1367726607509598</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.3749512076316971</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.5672100589225543</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.1796207309128991</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.2390973493135322</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.08728213348416371</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3355835834697822</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.01630809130386665</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>-0.03481557572741253</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.9504408258501056</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.7179456132896014</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1.528526964311381</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1339757936761107</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.9098474040393632</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-1.038924836372607</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.701052315013517</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.064870246136182</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.847365091994597</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.04501618610747</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2.94938363067129</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-7.330793745970504</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.581775281660572</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.145571317155526</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.507356247200626</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-5.031921873283268</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-1.196725228588095</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>4.715017988393709</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>10.88414144319029</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.490637911054725</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.654469695705866</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.535541255098519</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>7.437608700414873</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.06524768667024169</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.232437509765689</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.09330940226482036</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.1618756211138105</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.07646226183992504</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.215801962144522</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.3770653734064746</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.1430153158430371</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.4354942498571037</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.262247190182047</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3177590775797648</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.08180342522493071</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.3600551686140548</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.8235054136937391</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.4108548714377653</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.8313836492531871</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2049540411688643</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.6324247211132349</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>0.207266981733642</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>4.64564069542952</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.575543896436311</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>8.436144755710172</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.7735345994811071</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>6.512077621924822</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-6.260346526153657</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.868917746503042</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-7.089029117042567</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1.570086438793641</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-4.830909138414915</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>1.816927565554024</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>7.58465355366951</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>11.76493575978223</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.143453446120763</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>15.33917605393071</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>3.456934754792615</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>11.58003500975826</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.01415800189513093</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.3173346242601879</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.1457100750565327</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.7801948827466346</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.06063695733264418</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.5104782296388629</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.3519319117047235</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.1050030861368633</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.5010168480462076</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>0.09479333085672584</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.3344632712880309</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.1181854599540826</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.6852209093087388</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1.104269178765802</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.5470976710971147</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1.90234546371732</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.3476114235409222</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.12466508806785</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>3.74563313813477</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>12.32324258637117</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-8.732574771283565</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>4.631272890756296</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-1.79478354335663</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>8.72416648398444</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-4.210606773357433</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>5.156382073615744</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-16.95421962350886</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-4.137607534962529</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-7.389700775732264</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>3.231775670911597</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>11.23535530740828</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>20.01217805727726</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-0.8251489751354493</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>13.29765683792713</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>3.954885799375401</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>15.51688151418557</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.3860621969442512</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>1.270155920486261</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.6063296311899879</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.3215635774487285</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.1517216275129714</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.737495472667828</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.3293221702665068</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.3659653482475036</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.8729484616184263</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.2343930457485232</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.4822884700186743</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.2141201171306718</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>1.820903145874887</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>3.492097520732234</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.01359753682421944</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1.483440835019167</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.4498147534399919</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>1.841007361655972</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-1.788707130820175</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>5.423892034946295</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-0.9802866104399427</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>5.478024357987123</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-1.387184741203523</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>5.50742659533445</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-4.754374910265172</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>1.781932060309181</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-3.881932017854223</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>2.271533384404477</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-3.371524432020421</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>3.421742964140589</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>1.218639352659736</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>9.06579056802496</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>1.63239770877119</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>8.949089585591279</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.5780936406191431</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>8.130888357313456</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.1228535263644642</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.3725284322021704</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.08527806812046203</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.4765497451365999</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.1061805396290427</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.4215599483545328</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.2952424474177189</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.1035035838980895</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.299453071095587</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>0.1629626198262448</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.2393602870000293</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>0.241991579671097</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.09536336677632763</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.6951922013233559</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.1547721324951022</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.8570104279625712</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.04953506364176149</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.6895246299253732</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
